--- a/requirements/CTicket Requirements.xlsx
+++ b/requirements/CTicket Requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983FF463-37D3-42A8-8985-546C14118427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04F8705-1861-4C8A-8266-C8ACEDAB3B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{4F863675-D374-484B-B552-E0E525D01C14}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4F863675-D374-484B-B552-E0E525D01C14}"/>
   </bookViews>
   <sheets>
     <sheet name="Business Requirements" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="162">
   <si>
     <t>ID</t>
   </si>
@@ -245,15 +245,6 @@
     <t>Refund</t>
   </si>
   <si>
-    <t>Successfully purchased tickets shall not be cancelled or refunded except where the applicable event policy or CTicket's stated refund conditions allow it.</t>
-  </si>
-  <si>
-    <t>CTicket refund rules</t>
-  </si>
-  <si>
-    <t>If CTicket receives payment but cannot provide the purchased ticket due to a system error, the system shall initiate an automatic refund.</t>
-  </si>
-  <si>
     <t>R-023</t>
   </si>
   <si>
@@ -270,12 +261,6 @@
   </si>
   <si>
     <t>The system shall enforce any ticket quantity limits defined for the selected event.</t>
-  </si>
-  <si>
-    <t>R-025</t>
-  </si>
-  <si>
-    <t>R-026</t>
   </si>
   <si>
     <t>Language</t>
@@ -912,7 +897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75165FE8-34D7-4081-A864-79FBAD673BB9}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
@@ -922,7 +907,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
@@ -1118,7 +1103,7 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>67</v>
@@ -1252,57 +1237,29 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" t="s">
         <v>72</v>
-      </c>
-      <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1325,7 +1282,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
@@ -1339,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -1347,282 +1304,282 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s">
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s">
         <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
         <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
         <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B11" t="s">
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s">
         <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" t="s">
         <v>108</v>
       </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B16" t="s">
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C17" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1643,7 +1600,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
@@ -1654,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -1665,142 +1622,142 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C10" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C11" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C12" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
